--- a/artfynd/A 52676-2020 artfynd.xlsx
+++ b/artfynd/A 52676-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52676-2020 artfynd.xlsx
+++ b/artfynd/A 52676-2020 artfynd.xlsx
@@ -5377,10 +5377,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120856397</v>
+        <v>120856389</v>
       </c>
       <c r="B44" t="n">
-        <v>79679</v>
+        <v>79545</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5393,21 +5393,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5417,10 +5417,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>738163</v>
+        <v>738100</v>
       </c>
       <c r="R44" t="n">
-        <v>7060841</v>
+        <v>7060805</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5479,10 +5479,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120856389</v>
+        <v>120856397</v>
       </c>
       <c r="B45" t="n">
-        <v>79545</v>
+        <v>79679</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5495,21 +5495,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5519,10 +5519,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>738100</v>
+        <v>738163</v>
       </c>
       <c r="R45" t="n">
-        <v>7060805</v>
+        <v>7060841</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -6295,10 +6295,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120856417</v>
+        <v>120856412</v>
       </c>
       <c r="B53" t="n">
-        <v>78598</v>
+        <v>79639</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6307,25 +6307,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6335,10 +6335,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>738042</v>
+        <v>738133</v>
       </c>
       <c r="R53" t="n">
-        <v>7060655</v>
+        <v>7060822</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120856412</v>
+        <v>120856417</v>
       </c>
       <c r="B54" t="n">
-        <v>79639</v>
+        <v>78598</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6409,25 +6409,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6437,10 +6437,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>738133</v>
+        <v>738042</v>
       </c>
       <c r="R54" t="n">
-        <v>7060822</v>
+        <v>7060655</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>

--- a/artfynd/A 52676-2020 artfynd.xlsx
+++ b/artfynd/A 52676-2020 artfynd.xlsx
@@ -3949,10 +3949,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120856390</v>
+        <v>120856382</v>
       </c>
       <c r="B30" t="n">
-        <v>79545</v>
+        <v>90662</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3961,25 +3961,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>388</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>738107</v>
+        <v>738042</v>
       </c>
       <c r="R30" t="n">
-        <v>7060806</v>
+        <v>7060641</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4051,10 +4051,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120856380</v>
+        <v>120856398</v>
       </c>
       <c r="B31" t="n">
-        <v>90652</v>
+        <v>79682</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4063,25 +4063,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4091,10 +4091,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>738110</v>
+        <v>738140</v>
       </c>
       <c r="R31" t="n">
-        <v>7060773</v>
+        <v>7060812</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4153,10 +4153,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120856399</v>
+        <v>120856411</v>
       </c>
       <c r="B32" t="n">
-        <v>79679</v>
+        <v>79642</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4165,25 +4165,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>738120</v>
+        <v>738135</v>
       </c>
       <c r="R32" t="n">
-        <v>7060796</v>
+        <v>7060830</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4255,10 +4255,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120856396</v>
+        <v>120856392</v>
       </c>
       <c r="B33" t="n">
-        <v>79679</v>
+        <v>79586</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4267,25 +4267,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>738118</v>
+        <v>738090</v>
       </c>
       <c r="R33" t="n">
-        <v>7060729</v>
+        <v>7060802</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4357,10 +4357,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120856392</v>
+        <v>120856418</v>
       </c>
       <c r="B34" t="n">
-        <v>79583</v>
+        <v>78601</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4369,25 +4369,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>738090</v>
+        <v>737998</v>
       </c>
       <c r="R34" t="n">
-        <v>7060802</v>
+        <v>7060623</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4459,10 +4459,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120856418</v>
+        <v>120856405</v>
       </c>
       <c r="B35" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4475,21 +4475,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>737998</v>
+        <v>738092</v>
       </c>
       <c r="R35" t="n">
-        <v>7060623</v>
+        <v>7060809</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4561,10 +4561,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120856414</v>
+        <v>120856417</v>
       </c>
       <c r="B36" t="n">
-        <v>79639</v>
+        <v>78601</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4573,25 +4573,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>738106</v>
+        <v>738042</v>
       </c>
       <c r="R36" t="n">
-        <v>7060811</v>
+        <v>7060655</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4663,10 +4663,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120856413</v>
+        <v>120856402</v>
       </c>
       <c r="B37" t="n">
-        <v>79639</v>
+        <v>79682</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4675,25 +4675,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4706,7 +4706,7 @@
         <v>738103</v>
       </c>
       <c r="R37" t="n">
-        <v>7060818</v>
+        <v>7060808</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4765,10 +4765,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120856385</v>
+        <v>120856390</v>
       </c>
       <c r="B38" t="n">
-        <v>90687</v>
+        <v>79548</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4781,21 +4781,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>388</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>738124</v>
+        <v>738107</v>
       </c>
       <c r="R38" t="n">
-        <v>7060725</v>
+        <v>7060806</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120856382</v>
+        <v>120856380</v>
       </c>
       <c r="B39" t="n">
-        <v>90652</v>
+        <v>90662</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>738042</v>
+        <v>738110</v>
       </c>
       <c r="R39" t="n">
-        <v>7060641</v>
+        <v>7060773</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4969,10 +4969,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120856404</v>
+        <v>120856415</v>
       </c>
       <c r="B40" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4985,21 +4985,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>738099</v>
+        <v>738096</v>
       </c>
       <c r="R40" t="n">
-        <v>7060810</v>
+        <v>7060751</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5071,10 +5071,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120856416</v>
+        <v>120856403</v>
       </c>
       <c r="B41" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5087,21 +5087,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5111,10 +5111,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>738056</v>
+        <v>738100</v>
       </c>
       <c r="R41" t="n">
-        <v>7060762</v>
+        <v>7060806</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5173,10 +5173,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120856405</v>
+        <v>120856404</v>
       </c>
       <c r="B42" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>738092</v>
+        <v>738099</v>
       </c>
       <c r="R42" t="n">
-        <v>7060809</v>
+        <v>7060810</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5275,10 +5275,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120856388</v>
+        <v>120856414</v>
       </c>
       <c r="B43" t="n">
-        <v>79545</v>
+        <v>79642</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5287,25 +5287,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>388</v>
+        <v>229497</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5315,10 +5315,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>738127</v>
+        <v>738106</v>
       </c>
       <c r="R43" t="n">
-        <v>7060825</v>
+        <v>7060811</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5377,10 +5377,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120856389</v>
+        <v>120856407</v>
       </c>
       <c r="B44" t="n">
-        <v>79545</v>
+        <v>79642</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5389,25 +5389,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>388</v>
+        <v>229497</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5417,10 +5417,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>738100</v>
+        <v>738143</v>
       </c>
       <c r="R44" t="n">
-        <v>7060805</v>
+        <v>7060819</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5479,10 +5479,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120856397</v>
+        <v>120856401</v>
       </c>
       <c r="B45" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5519,10 +5519,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>738163</v>
+        <v>738103</v>
       </c>
       <c r="R45" t="n">
-        <v>7060841</v>
+        <v>7060815</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5581,10 +5581,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120856387</v>
+        <v>120856383</v>
       </c>
       <c r="B46" t="n">
-        <v>79545</v>
+        <v>90662</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5593,25 +5593,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>388</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5621,10 +5621,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>738128</v>
+        <v>738025</v>
       </c>
       <c r="R46" t="n">
-        <v>7060837</v>
+        <v>7060634</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5683,10 +5683,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120856383</v>
+        <v>120856387</v>
       </c>
       <c r="B47" t="n">
-        <v>90652</v>
+        <v>79548</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5695,25 +5695,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>388</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5723,10 +5723,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>738025</v>
+        <v>738128</v>
       </c>
       <c r="R47" t="n">
-        <v>7060634</v>
+        <v>7060837</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5785,10 +5785,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120856409</v>
+        <v>120856397</v>
       </c>
       <c r="B48" t="n">
-        <v>79639</v>
+        <v>79682</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5797,25 +5797,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>738151</v>
+        <v>738163</v>
       </c>
       <c r="R48" t="n">
-        <v>7060844</v>
+        <v>7060841</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5887,10 +5887,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120856407</v>
+        <v>120856412</v>
       </c>
       <c r="B49" t="n">
-        <v>79639</v>
+        <v>79642</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>738143</v>
+        <v>738133</v>
       </c>
       <c r="R49" t="n">
-        <v>7060819</v>
+        <v>7060822</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5989,10 +5989,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120856415</v>
+        <v>120856399</v>
       </c>
       <c r="B50" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6005,21 +6005,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6029,10 +6029,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>738096</v>
+        <v>738120</v>
       </c>
       <c r="R50" t="n">
-        <v>7060751</v>
+        <v>7060796</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6091,10 +6091,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120856402</v>
+        <v>120856385</v>
       </c>
       <c r="B51" t="n">
-        <v>79679</v>
+        <v>90697</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6107,21 +6107,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6131,10 +6131,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>738103</v>
+        <v>738124</v>
       </c>
       <c r="R51" t="n">
-        <v>7060808</v>
+        <v>7060725</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6193,10 +6193,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120856398</v>
+        <v>120856413</v>
       </c>
       <c r="B52" t="n">
-        <v>79679</v>
+        <v>79642</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6205,25 +6205,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6233,10 +6233,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>738140</v>
+        <v>738103</v>
       </c>
       <c r="R52" t="n">
-        <v>7060812</v>
+        <v>7060818</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6295,10 +6295,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120856412</v>
+        <v>120856381</v>
       </c>
       <c r="B53" t="n">
-        <v>79639</v>
+        <v>90662</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6311,21 +6311,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6335,10 +6335,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>738133</v>
+        <v>738116</v>
       </c>
       <c r="R53" t="n">
-        <v>7060822</v>
+        <v>7060802</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120856417</v>
+        <v>120856416</v>
       </c>
       <c r="B54" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6437,10 +6437,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>738042</v>
+        <v>738056</v>
       </c>
       <c r="R54" t="n">
-        <v>7060655</v>
+        <v>7060762</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6499,10 +6499,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120856403</v>
+        <v>120856409</v>
       </c>
       <c r="B55" t="n">
-        <v>79679</v>
+        <v>79642</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6511,25 +6511,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>738100</v>
+        <v>738151</v>
       </c>
       <c r="R55" t="n">
-        <v>7060806</v>
+        <v>7060844</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6601,10 +6601,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120856411</v>
+        <v>120856388</v>
       </c>
       <c r="B56" t="n">
-        <v>79639</v>
+        <v>79548</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6613,25 +6613,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229497</v>
+        <v>388</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>738135</v>
+        <v>738127</v>
       </c>
       <c r="R56" t="n">
-        <v>7060830</v>
+        <v>7060825</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6703,10 +6703,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120856401</v>
+        <v>120856396</v>
       </c>
       <c r="B57" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>738103</v>
+        <v>738118</v>
       </c>
       <c r="R57" t="n">
-        <v>7060815</v>
+        <v>7060729</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6805,10 +6805,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120856381</v>
+        <v>120856400</v>
       </c>
       <c r="B58" t="n">
-        <v>90652</v>
+        <v>79682</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6817,25 +6817,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6845,10 +6845,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>738116</v>
+        <v>738105</v>
       </c>
       <c r="R58" t="n">
-        <v>7060802</v>
+        <v>7060810</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6907,10 +6907,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120856400</v>
+        <v>120856389</v>
       </c>
       <c r="B59" t="n">
-        <v>79679</v>
+        <v>79548</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6923,21 +6923,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6947,10 +6947,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>738105</v>
+        <v>738100</v>
       </c>
       <c r="R59" t="n">
-        <v>7060810</v>
+        <v>7060805</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7012,7 +7012,7 @@
         <v>120856408</v>
       </c>
       <c r="B60" t="n">
-        <v>79639</v>
+        <v>79642</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>

--- a/artfynd/A 52676-2020 artfynd.xlsx
+++ b/artfynd/A 52676-2020 artfynd.xlsx
@@ -4867,10 +4867,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120856380</v>
+        <v>120856415</v>
       </c>
       <c r="B39" t="n">
-        <v>90662</v>
+        <v>78601</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4879,25 +4879,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>738110</v>
+        <v>738096</v>
       </c>
       <c r="R39" t="n">
-        <v>7060773</v>
+        <v>7060751</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4969,10 +4969,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120856415</v>
+        <v>120856403</v>
       </c>
       <c r="B40" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4985,21 +4985,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>738096</v>
+        <v>738100</v>
       </c>
       <c r="R40" t="n">
-        <v>7060751</v>
+        <v>7060806</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5071,7 +5071,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120856403</v>
+        <v>120856404</v>
       </c>
       <c r="B41" t="n">
         <v>79682</v>
@@ -5111,10 +5111,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>738100</v>
+        <v>738099</v>
       </c>
       <c r="R41" t="n">
-        <v>7060806</v>
+        <v>7060810</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5173,10 +5173,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120856404</v>
+        <v>120856380</v>
       </c>
       <c r="B42" t="n">
-        <v>79682</v>
+        <v>90662</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5185,25 +5185,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>738099</v>
+        <v>738110</v>
       </c>
       <c r="R42" t="n">
-        <v>7060810</v>
+        <v>7060773</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>

--- a/artfynd/A 52676-2020 artfynd.xlsx
+++ b/artfynd/A 52676-2020 artfynd.xlsx
@@ -6193,10 +6193,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120856413</v>
+        <v>120856381</v>
       </c>
       <c r="B52" t="n">
-        <v>79642</v>
+        <v>90662</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6209,21 +6209,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229497</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6233,10 +6233,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>738103</v>
+        <v>738116</v>
       </c>
       <c r="R52" t="n">
-        <v>7060818</v>
+        <v>7060802</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6295,10 +6295,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120856381</v>
+        <v>120856413</v>
       </c>
       <c r="B53" t="n">
-        <v>90662</v>
+        <v>79642</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6311,21 +6311,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>229497</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6335,10 +6335,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>738116</v>
+        <v>738103</v>
       </c>
       <c r="R53" t="n">
-        <v>7060802</v>
+        <v>7060818</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>

--- a/artfynd/A 52676-2020 artfynd.xlsx
+++ b/artfynd/A 52676-2020 artfynd.xlsx
@@ -3949,10 +3949,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120856382</v>
+        <v>120856389</v>
       </c>
       <c r="B30" t="n">
-        <v>90662</v>
+        <v>79548</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3961,25 +3961,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>388</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>738042</v>
+        <v>738100</v>
       </c>
       <c r="R30" t="n">
-        <v>7060641</v>
+        <v>7060805</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4051,7 +4051,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120856398</v>
+        <v>120856399</v>
       </c>
       <c r="B31" t="n">
         <v>79682</v>
@@ -4091,10 +4091,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>738140</v>
+        <v>738120</v>
       </c>
       <c r="R31" t="n">
-        <v>7060812</v>
+        <v>7060796</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4153,10 +4153,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120856411</v>
+        <v>120856392</v>
       </c>
       <c r="B32" t="n">
-        <v>79642</v>
+        <v>79586</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4169,21 +4169,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>738135</v>
+        <v>738090</v>
       </c>
       <c r="R32" t="n">
-        <v>7060830</v>
+        <v>7060802</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4255,10 +4255,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120856392</v>
+        <v>120856414</v>
       </c>
       <c r="B33" t="n">
-        <v>79586</v>
+        <v>79642</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4271,21 +4271,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>738090</v>
+        <v>738106</v>
       </c>
       <c r="R33" t="n">
-        <v>7060802</v>
+        <v>7060811</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4357,10 +4357,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120856418</v>
+        <v>120856413</v>
       </c>
       <c r="B34" t="n">
-        <v>78601</v>
+        <v>79642</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4369,25 +4369,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>737998</v>
+        <v>738103</v>
       </c>
       <c r="R34" t="n">
-        <v>7060623</v>
+        <v>7060818</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4459,10 +4459,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120856405</v>
+        <v>120856415</v>
       </c>
       <c r="B35" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4475,21 +4475,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>738092</v>
+        <v>738096</v>
       </c>
       <c r="R35" t="n">
-        <v>7060809</v>
+        <v>7060751</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4561,7 +4561,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120856417</v>
+        <v>120856418</v>
       </c>
       <c r="B36" t="n">
         <v>78601</v>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>738042</v>
+        <v>737998</v>
       </c>
       <c r="R36" t="n">
-        <v>7060655</v>
+        <v>7060623</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4663,7 +4663,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120856402</v>
+        <v>120856405</v>
       </c>
       <c r="B37" t="n">
         <v>79682</v>
@@ -4703,10 +4703,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>738103</v>
+        <v>738092</v>
       </c>
       <c r="R37" t="n">
-        <v>7060808</v>
+        <v>7060809</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4765,10 +4765,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120856390</v>
+        <v>120856403</v>
       </c>
       <c r="B38" t="n">
-        <v>79548</v>
+        <v>79682</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4781,21 +4781,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4805,7 +4805,7 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>738107</v>
+        <v>738100</v>
       </c>
       <c r="R38" t="n">
         <v>7060806</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120856415</v>
+        <v>120856387</v>
       </c>
       <c r="B39" t="n">
-        <v>78601</v>
+        <v>79548</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4883,21 +4883,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>388</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>738096</v>
+        <v>738128</v>
       </c>
       <c r="R39" t="n">
-        <v>7060751</v>
+        <v>7060837</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4969,10 +4969,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120856403</v>
+        <v>120856390</v>
       </c>
       <c r="B40" t="n">
-        <v>79682</v>
+        <v>79548</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4985,21 +4985,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>738100</v>
+        <v>738107</v>
       </c>
       <c r="R40" t="n">
         <v>7060806</v>
@@ -5071,10 +5071,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120856404</v>
+        <v>120856412</v>
       </c>
       <c r="B41" t="n">
-        <v>79682</v>
+        <v>79642</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5083,25 +5083,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5111,10 +5111,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>738099</v>
+        <v>738133</v>
       </c>
       <c r="R41" t="n">
-        <v>7060810</v>
+        <v>7060822</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5275,10 +5275,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120856414</v>
+        <v>120856417</v>
       </c>
       <c r="B43" t="n">
-        <v>79642</v>
+        <v>78601</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5287,25 +5287,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5315,10 +5315,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>738106</v>
+        <v>738042</v>
       </c>
       <c r="R43" t="n">
-        <v>7060811</v>
+        <v>7060655</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5377,10 +5377,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120856407</v>
+        <v>120856383</v>
       </c>
       <c r="B44" t="n">
-        <v>79642</v>
+        <v>90662</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5393,21 +5393,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229497</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5417,10 +5417,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>738143</v>
+        <v>738025</v>
       </c>
       <c r="R44" t="n">
-        <v>7060819</v>
+        <v>7060634</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5479,10 +5479,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120856401</v>
+        <v>120856416</v>
       </c>
       <c r="B45" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5495,21 +5495,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5519,10 +5519,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>738103</v>
+        <v>738056</v>
       </c>
       <c r="R45" t="n">
-        <v>7060815</v>
+        <v>7060762</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5581,10 +5581,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120856383</v>
+        <v>120856401</v>
       </c>
       <c r="B46" t="n">
-        <v>90662</v>
+        <v>79682</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5593,25 +5593,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5621,10 +5621,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>738025</v>
+        <v>738103</v>
       </c>
       <c r="R46" t="n">
-        <v>7060634</v>
+        <v>7060815</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5683,10 +5683,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120856387</v>
+        <v>120856385</v>
       </c>
       <c r="B47" t="n">
-        <v>79548</v>
+        <v>90697</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5699,21 +5699,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>388</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5723,10 +5723,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>738128</v>
+        <v>738124</v>
       </c>
       <c r="R47" t="n">
-        <v>7060837</v>
+        <v>7060725</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5785,7 +5785,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120856397</v>
+        <v>120856400</v>
       </c>
       <c r="B48" t="n">
         <v>79682</v>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>738163</v>
+        <v>738105</v>
       </c>
       <c r="R48" t="n">
-        <v>7060841</v>
+        <v>7060810</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5887,10 +5887,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120856412</v>
+        <v>120856388</v>
       </c>
       <c r="B49" t="n">
-        <v>79642</v>
+        <v>79548</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5899,25 +5899,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229497</v>
+        <v>388</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>738133</v>
+        <v>738127</v>
       </c>
       <c r="R49" t="n">
-        <v>7060822</v>
+        <v>7060825</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5989,10 +5989,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120856399</v>
+        <v>120856411</v>
       </c>
       <c r="B50" t="n">
-        <v>79682</v>
+        <v>79642</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6001,25 +6001,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6029,10 +6029,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>738120</v>
+        <v>738135</v>
       </c>
       <c r="R50" t="n">
-        <v>7060796</v>
+        <v>7060830</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6091,10 +6091,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120856385</v>
+        <v>120856407</v>
       </c>
       <c r="B51" t="n">
-        <v>90697</v>
+        <v>79642</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6103,25 +6103,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6131,10 +6131,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>738124</v>
+        <v>738143</v>
       </c>
       <c r="R51" t="n">
-        <v>7060725</v>
+        <v>7060819</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6295,10 +6295,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120856413</v>
+        <v>120856382</v>
       </c>
       <c r="B53" t="n">
-        <v>79642</v>
+        <v>90662</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6311,21 +6311,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6335,10 +6335,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>738103</v>
+        <v>738042</v>
       </c>
       <c r="R53" t="n">
-        <v>7060818</v>
+        <v>7060641</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120856416</v>
+        <v>120856409</v>
       </c>
       <c r="B54" t="n">
-        <v>78601</v>
+        <v>79642</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6409,25 +6409,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6437,10 +6437,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>738056</v>
+        <v>738151</v>
       </c>
       <c r="R54" t="n">
-        <v>7060762</v>
+        <v>7060844</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6499,10 +6499,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120856409</v>
+        <v>120856396</v>
       </c>
       <c r="B55" t="n">
-        <v>79642</v>
+        <v>79682</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6511,25 +6511,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>738151</v>
+        <v>738118</v>
       </c>
       <c r="R55" t="n">
-        <v>7060844</v>
+        <v>7060729</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6601,10 +6601,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120856388</v>
+        <v>120856404</v>
       </c>
       <c r="B56" t="n">
-        <v>79548</v>
+        <v>79682</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6617,21 +6617,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>738127</v>
+        <v>738099</v>
       </c>
       <c r="R56" t="n">
-        <v>7060825</v>
+        <v>7060810</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6703,10 +6703,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120856396</v>
+        <v>120856408</v>
       </c>
       <c r="B57" t="n">
-        <v>79682</v>
+        <v>79642</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6715,25 +6715,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>738118</v>
+        <v>738151</v>
       </c>
       <c r="R57" t="n">
-        <v>7060729</v>
+        <v>7060841</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6805,7 +6805,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120856400</v>
+        <v>120856397</v>
       </c>
       <c r="B58" t="n">
         <v>79682</v>
@@ -6845,10 +6845,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>738105</v>
+        <v>738163</v>
       </c>
       <c r="R58" t="n">
-        <v>7060810</v>
+        <v>7060841</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6907,10 +6907,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120856389</v>
+        <v>120856398</v>
       </c>
       <c r="B59" t="n">
-        <v>79548</v>
+        <v>79682</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6923,21 +6923,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6947,10 +6947,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>738100</v>
+        <v>738140</v>
       </c>
       <c r="R59" t="n">
-        <v>7060805</v>
+        <v>7060812</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7009,10 +7009,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120856408</v>
+        <v>120856402</v>
       </c>
       <c r="B60" t="n">
-        <v>79642</v>
+        <v>79682</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7021,25 +7021,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>738151</v>
+        <v>738103</v>
       </c>
       <c r="R60" t="n">
-        <v>7060841</v>
+        <v>7060808</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>

--- a/artfynd/A 52676-2020 artfynd.xlsx
+++ b/artfynd/A 52676-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7109,6 +7109,889 @@
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128492737</v>
+      </c>
+      <c r="B61" t="n">
+        <v>91859</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Rudtjärnsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>738090</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7060797</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128492744</v>
+      </c>
+      <c r="B62" t="n">
+        <v>82942</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Rudtjärnsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>738028</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7060769</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128492740</v>
+      </c>
+      <c r="B63" t="n">
+        <v>82942</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Rudtjärnsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>738118</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7060760</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128492741</v>
+      </c>
+      <c r="B64" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Rudtjärnsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>738094</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7060662</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128492735</v>
+      </c>
+      <c r="B65" t="n">
+        <v>75109</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Rudtjärnsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>738131</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7060820</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128492742</v>
+      </c>
+      <c r="B66" t="n">
+        <v>82942</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Rudtjärnsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>738074</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7060674</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128492736</v>
+      </c>
+      <c r="B67" t="n">
+        <v>91417</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Rudtjärnsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>738113</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7060795</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128492739</v>
+      </c>
+      <c r="B68" t="n">
+        <v>91452</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Rudtjärnsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>738089</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7060793</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128492738</v>
+      </c>
+      <c r="B69" t="n">
+        <v>91417</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Rudtjärnsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>738090</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7060795</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52676-2020 artfynd.xlsx
+++ b/artfynd/A 52676-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AY85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7992,6 +7992,1624 @@
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128627286</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>naturskog S Rudtjärnberget, Norrbyn, Ång</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>738049</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7060757</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128627292</v>
+      </c>
+      <c r="B71" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>naturskog S Rudtjärnberget, Norrbyn, Ång</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>738088</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7060809</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>död asp</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128627289</v>
+      </c>
+      <c r="B72" t="n">
+        <v>91452</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>naturskog S Rudtjärnberget, Norrbyn, Ång</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>738086</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7060792</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>128627299</v>
+      </c>
+      <c r="B73" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>naturskog S Rudtjärnberget, Norrbyn, Ång</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>738104</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7060804</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>128627295</v>
+      </c>
+      <c r="B74" t="n">
+        <v>91436</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Rävticka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Inocutis rheades</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>naturskog S Rudtjärnberget, Norrbyn, Ång</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>738101</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7060812</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>död asp</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>128627303</v>
+      </c>
+      <c r="B75" t="n">
+        <v>91417</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>naturskog S Rudtjärnberget, Norrbyn, Ång</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>738133</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7060810</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128627302</v>
+      </c>
+      <c r="B76" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>naturskog S Rudtjärnberget, Norrbyn, Ång</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>738134</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7060808</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>128627293</v>
+      </c>
+      <c r="B77" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>naturskog S Rudtjärnberget, Norrbyn, Ång</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>738099</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7060812</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128627296</v>
+      </c>
+      <c r="B78" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>naturskog S Rudtjärnberget, Norrbyn, Ång</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>738102</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7060809</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>död asp</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>128627288</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>naturskog S Rudtjärnberget, Norrbyn, Ång</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>738072</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7060775</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128627304</v>
+      </c>
+      <c r="B80" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>naturskog S Rudtjärnberget, Norrbyn, Ång</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>738132</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7060822</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128627285</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>naturskog S Rudtjärnberget, Norrbyn, Ång</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>738043</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7060743</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128627291</v>
+      </c>
+      <c r="B82" t="n">
+        <v>91505</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>naturskog S Rudtjärnberget, Norrbyn, Ång</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>738088</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7060809</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>död asp</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128627284</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>naturskog S Rudtjärnberget, Norrbyn, Ång</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>738025</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7060725</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128627297</v>
+      </c>
+      <c r="B84" t="n">
+        <v>4870</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>101675</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Aspvedgnagare</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Ptilinus fuscus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Geoffroy, 1785)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>naturskog S Rudtjärnberget, Norrbyn, Ång</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>738102</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7060809</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>död asp</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>128627300</v>
+      </c>
+      <c r="B85" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>naturskog S Rudtjärnberget, Norrbyn, Ång</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>738105</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7060800</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52676-2020 artfynd.xlsx
+++ b/artfynd/A 52676-2020 artfynd.xlsx
@@ -9403,50 +9403,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128627297</v>
+        <v>128627300</v>
       </c>
       <c r="B84" t="n">
-        <v>4870</v>
+        <v>80188</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>101675</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>naturskog S Rudtjärnberget, Norrbyn, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>738102</v>
+        <v>738105</v>
       </c>
       <c r="R84" t="n">
-        <v>7060809</v>
+        <v>7060800</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9492,7 +9487,7 @@
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>död asp</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -9510,45 +9505,50 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128627300</v>
+        <v>128627297</v>
       </c>
       <c r="B85" t="n">
-        <v>80188</v>
+        <v>4870</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>101675</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>naturskog S Rudtjärnberget, Norrbyn, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>738105</v>
+        <v>738102</v>
       </c>
       <c r="R85" t="n">
-        <v>7060800</v>
+        <v>7060809</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9594,7 +9594,7 @@
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>död asp</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>

--- a/artfynd/A 52676-2020 artfynd.xlsx
+++ b/artfynd/A 52676-2020 artfynd.xlsx
@@ -7114,7 +7114,7 @@
         <v>128492737</v>
       </c>
       <c r="B61" t="n">
-        <v>91859</v>
+        <v>91865</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>128492744</v>
       </c>
       <c r="B62" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>128492740</v>
       </c>
       <c r="B63" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>128492741</v>
       </c>
       <c r="B64" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>128492735</v>
       </c>
       <c r="B65" t="n">
-        <v>75109</v>
+        <v>75113</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>128492742</v>
       </c>
       <c r="B66" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>128492736</v>
       </c>
       <c r="B67" t="n">
-        <v>91417</v>
+        <v>91423</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>128492739</v>
       </c>
       <c r="B68" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>128492738</v>
       </c>
       <c r="B69" t="n">
-        <v>91417</v>
+        <v>91423</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>128627286</v>
       </c>
       <c r="B70" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>128627292</v>
       </c>
       <c r="B71" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>128627289</v>
       </c>
       <c r="B72" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>128627299</v>
       </c>
       <c r="B73" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>128627295</v>
       </c>
       <c r="B74" t="n">
-        <v>91436</v>
+        <v>91442</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>128627303</v>
       </c>
       <c r="B75" t="n">
-        <v>91417</v>
+        <v>91423</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>128627302</v>
       </c>
       <c r="B76" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>128627293</v>
       </c>
       <c r="B77" t="n">
-        <v>80148</v>
+        <v>80152</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>128627296</v>
       </c>
       <c r="B78" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>128627288</v>
       </c>
       <c r="B79" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>128627304</v>
       </c>
       <c r="B80" t="n">
-        <v>80148</v>
+        <v>80152</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>128627285</v>
       </c>
       <c r="B81" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>128627291</v>
       </c>
       <c r="B82" t="n">
-        <v>91505</v>
+        <v>91511</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>128627284</v>
       </c>
       <c r="B83" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>128627300</v>
       </c>
       <c r="B84" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 52676-2020 artfynd.xlsx
+++ b/artfynd/A 52676-2020 artfynd.xlsx
@@ -7114,7 +7114,7 @@
         <v>128492737</v>
       </c>
       <c r="B61" t="n">
-        <v>91865</v>
+        <v>91871</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>128492736</v>
       </c>
       <c r="B67" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>128492739</v>
       </c>
       <c r="B68" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>128492738</v>
       </c>
       <c r="B69" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>128627289</v>
       </c>
       <c r="B72" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>128627295</v>
       </c>
       <c r="B74" t="n">
-        <v>91442</v>
+        <v>91448</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>128627303</v>
       </c>
       <c r="B75" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>128627291</v>
       </c>
       <c r="B82" t="n">
-        <v>91511</v>
+        <v>91517</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 52676-2020 artfynd.xlsx
+++ b/artfynd/A 52676-2020 artfynd.xlsx
@@ -7114,7 +7114,7 @@
         <v>128492737</v>
       </c>
       <c r="B61" t="n">
-        <v>91871</v>
+        <v>91873</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>128492744</v>
       </c>
       <c r="B62" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>128492740</v>
       </c>
       <c r="B63" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>128492741</v>
       </c>
       <c r="B64" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>128492735</v>
       </c>
       <c r="B65" t="n">
-        <v>75113</v>
+        <v>75115</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>128492742</v>
       </c>
       <c r="B66" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>128492736</v>
       </c>
       <c r="B67" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>128492739</v>
       </c>
       <c r="B68" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>128492738</v>
       </c>
       <c r="B69" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>128627286</v>
       </c>
       <c r="B70" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>128627292</v>
       </c>
       <c r="B71" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>128627289</v>
       </c>
       <c r="B72" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>128627299</v>
       </c>
       <c r="B73" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>128627295</v>
       </c>
       <c r="B74" t="n">
-        <v>91448</v>
+        <v>91450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>128627303</v>
       </c>
       <c r="B75" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>128627302</v>
       </c>
       <c r="B76" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>128627293</v>
       </c>
       <c r="B77" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>128627296</v>
       </c>
       <c r="B78" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>128627288</v>
       </c>
       <c r="B79" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>128627304</v>
       </c>
       <c r="B80" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>128627285</v>
       </c>
       <c r="B81" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>128627291</v>
       </c>
       <c r="B82" t="n">
-        <v>91517</v>
+        <v>91519</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>128627284</v>
       </c>
       <c r="B83" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>128627300</v>
       </c>
       <c r="B84" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 52676-2020 artfynd.xlsx
+++ b/artfynd/A 52676-2020 artfynd.xlsx
@@ -7397,32 +7397,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128492741</v>
+        <v>128492735</v>
       </c>
       <c r="B64" t="n">
-        <v>80194</v>
+        <v>75115</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>738094</v>
+        <v>738131</v>
       </c>
       <c r="R64" t="n">
-        <v>7060662</v>
+        <v>7060820</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7478,21 +7478,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7509,32 +7494,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128492735</v>
+        <v>128492741</v>
       </c>
       <c r="B65" t="n">
-        <v>75115</v>
+        <v>80194</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6426</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7544,10 +7529,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>738131</v>
+        <v>738094</v>
       </c>
       <c r="R65" t="n">
-        <v>7060820</v>
+        <v>7060662</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7590,6 +7575,21 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">

--- a/artfynd/A 52676-2020 artfynd.xlsx
+++ b/artfynd/A 52676-2020 artfynd.xlsx
@@ -7114,7 +7114,7 @@
         <v>128492737</v>
       </c>
       <c r="B61" t="n">
-        <v>91873</v>
+        <v>91874</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>128492736</v>
       </c>
       <c r="B67" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>128492739</v>
       </c>
       <c r="B68" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>128492738</v>
       </c>
       <c r="B69" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>128627289</v>
       </c>
       <c r="B72" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>128627295</v>
       </c>
       <c r="B74" t="n">
-        <v>91450</v>
+        <v>91451</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>128627303</v>
       </c>
       <c r="B75" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>128627291</v>
       </c>
       <c r="B82" t="n">
-        <v>91519</v>
+        <v>91520</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 52676-2020 artfynd.xlsx
+++ b/artfynd/A 52676-2020 artfynd.xlsx
@@ -7114,7 +7114,7 @@
         <v>128492737</v>
       </c>
       <c r="B61" t="n">
-        <v>91874</v>
+        <v>91901</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>128492744</v>
       </c>
       <c r="B62" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>128492740</v>
       </c>
       <c r="B63" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7397,32 +7397,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128492735</v>
+        <v>128492741</v>
       </c>
       <c r="B64" t="n">
-        <v>75115</v>
+        <v>80221</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6426</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>738131</v>
+        <v>738094</v>
       </c>
       <c r="R64" t="n">
-        <v>7060820</v>
+        <v>7060662</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7478,6 +7478,21 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7494,32 +7509,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128492741</v>
+        <v>128492735</v>
       </c>
       <c r="B65" t="n">
-        <v>80194</v>
+        <v>75142</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7529,10 +7544,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>738094</v>
+        <v>738131</v>
       </c>
       <c r="R65" t="n">
-        <v>7060662</v>
+        <v>7060820</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7575,21 +7590,6 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7609,7 +7609,7 @@
         <v>128492742</v>
       </c>
       <c r="B66" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>128492736</v>
       </c>
       <c r="B67" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>128492739</v>
       </c>
       <c r="B68" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>128492738</v>
       </c>
       <c r="B69" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>128627286</v>
       </c>
       <c r="B70" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>128627292</v>
       </c>
       <c r="B71" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>128627289</v>
       </c>
       <c r="B72" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>128627299</v>
       </c>
       <c r="B73" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>128627295</v>
       </c>
       <c r="B74" t="n">
-        <v>91451</v>
+        <v>91478</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>128627303</v>
       </c>
       <c r="B75" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>128627302</v>
       </c>
       <c r="B76" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>128627293</v>
       </c>
       <c r="B77" t="n">
-        <v>80154</v>
+        <v>80181</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>128627296</v>
       </c>
       <c r="B78" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>128627288</v>
       </c>
       <c r="B79" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>128627304</v>
       </c>
       <c r="B80" t="n">
-        <v>80154</v>
+        <v>80181</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>128627285</v>
       </c>
       <c r="B81" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>128627291</v>
       </c>
       <c r="B82" t="n">
-        <v>91520</v>
+        <v>91547</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>128627284</v>
       </c>
       <c r="B83" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>128627300</v>
       </c>
       <c r="B84" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 52676-2020 artfynd.xlsx
+++ b/artfynd/A 52676-2020 artfynd.xlsx
@@ -7114,7 +7114,7 @@
         <v>128492737</v>
       </c>
       <c r="B61" t="n">
-        <v>91901</v>
+        <v>91906</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>128492744</v>
       </c>
       <c r="B62" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>128492740</v>
       </c>
       <c r="B63" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>128492741</v>
       </c>
       <c r="B64" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>128492735</v>
       </c>
       <c r="B65" t="n">
-        <v>75142</v>
+        <v>75143</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>128492742</v>
       </c>
       <c r="B66" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>128492736</v>
       </c>
       <c r="B67" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>128492739</v>
       </c>
       <c r="B68" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>128492738</v>
       </c>
       <c r="B69" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>128627286</v>
       </c>
       <c r="B70" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>128627292</v>
       </c>
       <c r="B71" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>128627289</v>
       </c>
       <c r="B72" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>128627299</v>
       </c>
       <c r="B73" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>128627295</v>
       </c>
       <c r="B74" t="n">
-        <v>91478</v>
+        <v>91483</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>128627303</v>
       </c>
       <c r="B75" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>128627302</v>
       </c>
       <c r="B76" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>128627293</v>
       </c>
       <c r="B77" t="n">
-        <v>80181</v>
+        <v>80185</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>128627296</v>
       </c>
       <c r="B78" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>128627288</v>
       </c>
       <c r="B79" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>128627304</v>
       </c>
       <c r="B80" t="n">
-        <v>80181</v>
+        <v>80185</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>128627285</v>
       </c>
       <c r="B81" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>128627291</v>
       </c>
       <c r="B82" t="n">
-        <v>91547</v>
+        <v>91552</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>128627284</v>
       </c>
       <c r="B83" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>128627300</v>
       </c>
       <c r="B84" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 52676-2020 artfynd.xlsx
+++ b/artfynd/A 52676-2020 artfynd.xlsx
@@ -7114,7 +7114,7 @@
         <v>128492737</v>
       </c>
       <c r="B61" t="n">
-        <v>91906</v>
+        <v>91911</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>128492736</v>
       </c>
       <c r="B67" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>128492739</v>
       </c>
       <c r="B68" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>128492738</v>
       </c>
       <c r="B69" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>128627289</v>
       </c>
       <c r="B72" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>128627295</v>
       </c>
       <c r="B74" t="n">
-        <v>91483</v>
+        <v>91488</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>128627303</v>
       </c>
       <c r="B75" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>128627291</v>
       </c>
       <c r="B82" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 52676-2020 artfynd.xlsx
+++ b/artfynd/A 52676-2020 artfynd.xlsx
@@ -7114,7 +7114,7 @@
         <v>128492737</v>
       </c>
       <c r="B61" t="n">
-        <v>91911</v>
+        <v>91915</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>128492744</v>
       </c>
       <c r="B62" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>128492740</v>
       </c>
       <c r="B63" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>128492741</v>
       </c>
       <c r="B64" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>128492735</v>
       </c>
       <c r="B65" t="n">
-        <v>75143</v>
+        <v>75147</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>128492742</v>
       </c>
       <c r="B66" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>128492736</v>
       </c>
       <c r="B67" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>128492739</v>
       </c>
       <c r="B68" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>128492738</v>
       </c>
       <c r="B69" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>128627286</v>
       </c>
       <c r="B70" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>128627292</v>
       </c>
       <c r="B71" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>128627289</v>
       </c>
       <c r="B72" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>128627299</v>
       </c>
       <c r="B73" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>128627295</v>
       </c>
       <c r="B74" t="n">
-        <v>91488</v>
+        <v>91492</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>128627303</v>
       </c>
       <c r="B75" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>128627302</v>
       </c>
       <c r="B76" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>128627293</v>
       </c>
       <c r="B77" t="n">
-        <v>80185</v>
+        <v>80189</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>128627296</v>
       </c>
       <c r="B78" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>128627288</v>
       </c>
       <c r="B79" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>128627304</v>
       </c>
       <c r="B80" t="n">
-        <v>80185</v>
+        <v>80189</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>128627285</v>
       </c>
       <c r="B81" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>128627291</v>
       </c>
       <c r="B82" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>128627284</v>
       </c>
       <c r="B83" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>128627300</v>
       </c>
       <c r="B84" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 52676-2020 artfynd.xlsx
+++ b/artfynd/A 52676-2020 artfynd.xlsx
@@ -7114,7 +7114,7 @@
         <v>128492737</v>
       </c>
       <c r="B61" t="n">
-        <v>91915</v>
+        <v>91920</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>128492744</v>
       </c>
       <c r="B62" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>128492740</v>
       </c>
       <c r="B63" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>128492741</v>
       </c>
       <c r="B64" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>128492735</v>
       </c>
       <c r="B65" t="n">
-        <v>75147</v>
+        <v>75150</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>128492742</v>
       </c>
       <c r="B66" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>128492736</v>
       </c>
       <c r="B67" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>128492739</v>
       </c>
       <c r="B68" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>128492738</v>
       </c>
       <c r="B69" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>128627286</v>
       </c>
       <c r="B70" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>128627292</v>
       </c>
       <c r="B71" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>128627289</v>
       </c>
       <c r="B72" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>128627299</v>
       </c>
       <c r="B73" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>128627295</v>
       </c>
       <c r="B74" t="n">
-        <v>91492</v>
+        <v>91497</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>128627303</v>
       </c>
       <c r="B75" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>128627302</v>
       </c>
       <c r="B76" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>128627293</v>
       </c>
       <c r="B77" t="n">
-        <v>80189</v>
+        <v>80094</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>128627296</v>
       </c>
       <c r="B78" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>128627288</v>
       </c>
       <c r="B79" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>128627304</v>
       </c>
       <c r="B80" t="n">
-        <v>80189</v>
+        <v>80094</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>128627285</v>
       </c>
       <c r="B81" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>128627291</v>
       </c>
       <c r="B82" t="n">
-        <v>91561</v>
+        <v>91566</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>128627284</v>
       </c>
       <c r="B83" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>128627300</v>
       </c>
       <c r="B84" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
